--- a/artfynd/A 49178-2024 artfynd.xlsx
+++ b/artfynd/A 49178-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>402496</v>
+        <v>319542</v>
       </c>
       <c r="B2" t="n">
-        <v>81235</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1312</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>488167.224422015</v>
+        <v>488141</v>
       </c>
       <c r="R2" t="n">
-        <v>7091936.356419221</v>
+        <v>7092047</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +743,9 @@
           <t>2008-08-16</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2008-08-16</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -801,15 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>530298</v>
+        <v>402496</v>
       </c>
       <c r="B3" t="n">
-        <v>89405</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,37 +797,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1204</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Långberget, Jmt</t>
+          <t>Småhöjderna, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>487830.6508332609</v>
+        <v>488167</v>
       </c>
       <c r="R3" t="n">
-        <v>7092416.268569467</v>
+        <v>7091936</v>
       </c>
       <c r="S3" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -871,27 +851,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>1996-10-22</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2008-08-16</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1996-10-22</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Anm: Liggande stam. Källa: Skogsstyrelsens nyckelbiotopsregister</t>
+          <t>2008-08-16</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,40 +868,39 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Barrskog bergbrant</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>gran</t>
+          <t>Grannaturskog</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Dan Olofsson</t>
+          <t>Olli Manninen</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Olli Manninen, * Naturskyddare</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Naturskyddare</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>348534</v>
+        <v>142550</v>
       </c>
       <c r="B4" t="n">
-        <v>89405</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91859</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -944,21 +908,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1204</v>
+        <v>112</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -968,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>487589.787269201</v>
+        <v>487511</v>
       </c>
       <c r="R4" t="n">
-        <v>7091600.134757688</v>
+        <v>7091536</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1001,21 +965,11 @@
           <t>2008-08-16</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2008-08-16</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1035,42 +989,34 @@
           <t>Grannaturskog</t>
         </is>
       </c>
-      <c r="AN4" t="n">
-        <v>2</v>
-      </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>2 substratenheter # Granlåga</t>
+          <t>Granlåga</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Olli Manninen</t>
+          <t>Sten Svantesson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Olli Manninen, * Naturskyddare</t>
+          <t>Sten Svantesson, * Naturskyddare</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>Naturskyddare</t>
+          <t>Naturskyddare (204)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>348535</v>
+        <v>142551</v>
       </c>
       <c r="B5" t="n">
-        <v>89405</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91859</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1078,21 +1024,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1204</v>
+        <v>112</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1102,10 +1048,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>487654.2348935539</v>
+        <v>487505</v>
       </c>
       <c r="R5" t="n">
-        <v>7092203.810606843</v>
+        <v>7091528</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1135,19 +1081,9 @@
           <t>2008-08-16</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2008-08-16</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1177,31 +1113,26 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Olli Manninen</t>
+          <t>Sten Svantesson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Olli Manninen, * Naturskyddare</t>
+          <t>Sten Svantesson, * Naturskyddare</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>Naturskyddare</t>
+          <t>Naturskyddare (204)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>348536</v>
+        <v>235010</v>
       </c>
       <c r="B6" t="n">
-        <v>89405</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1209,21 +1140,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1204</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1233,10 +1164,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>487645.0456927472</v>
+        <v>487491</v>
       </c>
       <c r="R6" t="n">
-        <v>7092217.031906352</v>
+        <v>7091622</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1266,19 +1197,9 @@
           <t>2008-08-16</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2008-08-16</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1308,53 +1229,48 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Olli Manninen</t>
+          <t>Sten Svantesson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Olli Manninen, * Naturskyddare</t>
+          <t>Sten Svantesson, * Naturskyddare</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>Naturskyddare</t>
+          <t>Naturskyddare (204)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>833532</v>
+        <v>348822</v>
       </c>
       <c r="B7" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2081</v>
+        <v>1204</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1364,10 +1280,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>487544.5447799161</v>
+        <v>487562</v>
       </c>
       <c r="R7" t="n">
-        <v>7091623.61267647</v>
+        <v>7091521</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1397,21 +1313,11 @@
           <t>2008-08-16</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2008-08-16</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1433,7 +1339,7 @@
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Sälgstam</t>
+          <t>Granlåga</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1455,19 +1361,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>348829</v>
+        <v>348823</v>
       </c>
       <c r="B8" t="n">
-        <v>89405</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1495,10 +1396,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>487584.5770893861</v>
+        <v>487526</v>
       </c>
       <c r="R8" t="n">
-        <v>7091618.178377171</v>
+        <v>7091519</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1528,19 +1429,9 @@
           <t>2008-08-16</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2008-08-16</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1586,19 +1477,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>348828</v>
+        <v>348824</v>
       </c>
       <c r="B9" t="n">
-        <v>89405</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1626,10 +1512,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>487482.7096218006</v>
+        <v>487510</v>
       </c>
       <c r="R9" t="n">
-        <v>7091680.125702496</v>
+        <v>7091525</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1659,19 +1545,9 @@
           <t>2008-08-16</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2008-08-16</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1717,19 +1593,14 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>348836</v>
+        <v>348825</v>
       </c>
       <c r="B10" t="n">
-        <v>89405</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1757,10 +1628,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>488011.6627306363</v>
+        <v>487442</v>
       </c>
       <c r="R10" t="n">
-        <v>7091768.602275774</v>
+        <v>7091552</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1790,19 +1661,9 @@
           <t>2008-08-16</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2008-08-16</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1848,37 +1709,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>235010</v>
+        <v>348826</v>
       </c>
       <c r="B11" t="n">
-        <v>89672</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>1204</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1888,10 +1744,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>487490.8399551582</v>
+        <v>487513</v>
       </c>
       <c r="R11" t="n">
-        <v>7091622.068885379</v>
+        <v>7091640</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1921,19 +1777,9 @@
           <t>2008-08-16</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2008-08-16</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1979,19 +1825,14 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>348830</v>
+        <v>348827</v>
       </c>
       <c r="B12" t="n">
-        <v>89405</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -2019,10 +1860,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>487589.8274232431</v>
+        <v>487489</v>
       </c>
       <c r="R12" t="n">
-        <v>7091610.245030753</v>
+        <v>7091675</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -2052,19 +1893,9 @@
           <t>2008-08-16</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2008-08-16</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2110,19 +1941,14 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>348826</v>
+        <v>348828</v>
       </c>
       <c r="B13" t="n">
-        <v>89405</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -2150,10 +1976,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>487513.361179291</v>
+        <v>487483</v>
       </c>
       <c r="R13" t="n">
-        <v>7091640.441186843</v>
+        <v>7091680</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2183,19 +2009,9 @@
           <t>2008-08-16</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2008-08-16</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2241,15 +2057,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>348831</v>
+        <v>833532</v>
       </c>
       <c r="B14" t="n">
-        <v>89405</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2257,21 +2068,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1204</v>
+        <v>2081</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2281,10 +2092,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>487608.4269349267</v>
+        <v>487545</v>
       </c>
       <c r="R14" t="n">
-        <v>7091638.744000413</v>
+        <v>7091624</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2314,21 +2125,11 @@
           <t>2008-08-16</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2008-08-16</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2350,7 +2151,7 @@
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Granlåga</t>
+          <t>Sälgstam</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2372,15 +2173,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>348827</v>
+        <v>142552</v>
       </c>
       <c r="B15" t="n">
-        <v>89405</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91859</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2388,21 +2184,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1204</v>
+        <v>112</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2412,10 +2208,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>487488.8504311747</v>
+        <v>487657</v>
       </c>
       <c r="R15" t="n">
-        <v>7091674.826220323</v>
+        <v>7091612</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2445,19 +2241,9 @@
           <t>2008-08-16</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2008-08-16</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2496,6 +2282,1169 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr">
+        <is>
+          <t>Naturskyddare (204)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>348533</v>
+      </c>
+      <c r="B16" t="n">
+        <v>91923</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Småhöjderna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>487638</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7091600</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Laxsjö</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2008-08-16</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2008-08-16</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>Grannaturskog</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Olli Manninen</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Olli Manninen, * Naturskyddare</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Naturskyddare</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>348534</v>
+      </c>
+      <c r="B17" t="n">
+        <v>91923</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Småhöjderna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>487590</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7091600</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Laxsjö</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2008-08-16</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2008-08-16</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Grannaturskog</t>
+        </is>
+      </c>
+      <c r="AN17" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>2 substratenheter # Granlåga</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Olli Manninen</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Olli Manninen, * Naturskyddare</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Naturskyddare</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>348535</v>
+      </c>
+      <c r="B18" t="n">
+        <v>91923</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Småhöjderna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>487654</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7092204</v>
+      </c>
+      <c r="S18" t="n">
+        <v>25</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Laxsjö</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2008-08-16</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2008-08-16</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>Grannaturskog</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Olli Manninen</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Olli Manninen, * Naturskyddare</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Naturskyddare</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>348536</v>
+      </c>
+      <c r="B19" t="n">
+        <v>91923</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Småhöjderna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>487645</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7092217</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Laxsjö</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2008-08-16</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2008-08-16</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>Grannaturskog</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Olli Manninen</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Olli Manninen, * Naturskyddare</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Naturskyddare</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>348829</v>
+      </c>
+      <c r="B20" t="n">
+        <v>91923</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Småhöjderna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>487585</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7091618</v>
+      </c>
+      <c r="S20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Laxsjö</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2008-08-16</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2008-08-16</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>Grannaturskog</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Sten Svantesson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Sten Svantesson, * Naturskyddare</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Naturskyddare (204)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>348830</v>
+      </c>
+      <c r="B21" t="n">
+        <v>91923</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Småhöjderna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>487590</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7091610</v>
+      </c>
+      <c r="S21" t="n">
+        <v>25</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Laxsjö</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2008-08-16</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2008-08-16</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>Grannaturskog</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Sten Svantesson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Sten Svantesson, * Naturskyddare</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>Naturskyddare (204)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>348831</v>
+      </c>
+      <c r="B22" t="n">
+        <v>91923</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Småhöjderna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>487608</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7091639</v>
+      </c>
+      <c r="S22" t="n">
+        <v>25</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Laxsjö</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2008-08-16</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2008-08-16</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>Grannaturskog</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Sten Svantesson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Sten Svantesson, * Naturskyddare</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>Naturskyddare (204)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>348833</v>
+      </c>
+      <c r="B23" t="n">
+        <v>91923</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Småhöjderna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>487695</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7091680</v>
+      </c>
+      <c r="S23" t="n">
+        <v>25</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Laxsjö</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2008-08-16</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2008-08-16</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>Grannaturskog</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Sten Svantesson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Sten Svantesson, * Naturskyddare</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>Naturskyddare (204)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>348834</v>
+      </c>
+      <c r="B24" t="n">
+        <v>91923</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Småhöjderna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>487816</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7091703</v>
+      </c>
+      <c r="S24" t="n">
+        <v>25</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Laxsjö</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2008-08-16</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2008-08-16</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>Grannaturskog</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Sten Svantesson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Sten Svantesson, * Naturskyddare</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>Naturskyddare (204)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>348836</v>
+      </c>
+      <c r="B25" t="n">
+        <v>91923</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Småhöjderna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>488012</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7091769</v>
+      </c>
+      <c r="S25" t="n">
+        <v>25</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Laxsjö</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2008-08-16</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2008-08-16</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>Grannaturskog</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Sten Svantesson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Sten Svantesson, * Naturskyddare</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
         <is>
           <t>Naturskyddare (204)</t>
         </is>

--- a/artfynd/A 49178-2024 artfynd.xlsx
+++ b/artfynd/A 49178-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AZ25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
           <t>Naturskyddare</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/319542</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
           <t>Naturskyddare</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/402496</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1010,6 +1025,11 @@
           <t>Naturskyddare (204)</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/142550</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1126,6 +1146,11 @@
           <t>Naturskyddare (204)</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/142551</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1242,6 +1267,11 @@
           <t>Naturskyddare (204)</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/142552</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1358,6 +1388,11 @@
           <t>Naturskyddare (204)</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/235010</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1474,6 +1509,11 @@
           <t>Naturskyddare</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/348533</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1593,6 +1633,11 @@
           <t>Naturskyddare</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/348534</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1709,6 +1754,11 @@
           <t>Naturskyddare</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/348535</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1825,6 +1875,11 @@
           <t>Naturskyddare</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/348536</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1941,6 +1996,11 @@
           <t>Naturskyddare (204)</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/348822</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2057,6 +2117,11 @@
           <t>Naturskyddare (204)</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/348823</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2173,6 +2238,11 @@
           <t>Naturskyddare (204)</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/348824</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2289,6 +2359,11 @@
           <t>Naturskyddare (204)</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/348825</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2405,6 +2480,11 @@
           <t>Naturskyddare (204)</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/348826</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2521,6 +2601,11 @@
           <t>Naturskyddare (204)</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/348827</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2637,6 +2722,11 @@
           <t>Naturskyddare (204)</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/348828</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2753,6 +2843,11 @@
           <t>Naturskyddare (204)</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/348829</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2869,6 +2964,11 @@
           <t>Naturskyddare (204)</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/348830</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2985,6 +3085,11 @@
           <t>Naturskyddare (204)</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/348831</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3101,6 +3206,11 @@
           <t>Naturskyddare (204)</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/348833</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3217,6 +3327,11 @@
           <t>Naturskyddare (204)</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/348834</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3333,6 +3448,11 @@
           <t>Naturskyddare (204)</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/348836</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3449,8 +3569,39 @@
           <t>Naturskyddare (204)</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/833532</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>